--- a/data/trans_bre/IP15-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,49 +660,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 13,53</t>
+          <t>-9,29; 13,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 13,68</t>
+          <t>-13,79; 12,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 11,53</t>
+          <t>-15,26; 11,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 32,75</t>
+          <t>-1,91; 29,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-39,26; 88,54</t>
+          <t>-38,32; 98,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,25; 63,57</t>
+          <t>-40,98; 58,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-40,41; 49,93</t>
+          <t>-41,24; 54,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 146,14</t>
+          <t>-7,14; 124,77</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 6,14</t>
+          <t>-9,87; 7,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 9,68</t>
+          <t>-10,24; 9,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 17,2</t>
+          <t>-2,32; 15,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 44,5</t>
+          <t>-3,68; 42,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,44; 47,23</t>
+          <t>-45,54; 52,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,79; 54,42</t>
+          <t>-39,07; 52,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 116,05</t>
+          <t>-9,47; 110,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 138,34</t>
+          <t>-9,7; 147,71</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 12,47</t>
+          <t>-7,55; 12,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,03; 3,03</t>
+          <t>-21,38; 3,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 12,23</t>
+          <t>-6,23; 11,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 14,09</t>
+          <t>-12,28; 14,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-40,12; 123,64</t>
+          <t>-40,82; 137,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-56,67; 13,63</t>
+          <t>-55,53; 15,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-50,09; 150,4</t>
+          <t>-41,17; 152,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-35,51; 61,36</t>
+          <t>-33,66; 61,41</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 12,14</t>
+          <t>-9,73; 12,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 17,23</t>
+          <t>-4,57; 16,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 12,35</t>
+          <t>-12,94; 12,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 15,79</t>
+          <t>-8,17; 14,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 75,96</t>
+          <t>-38,3; 80,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,19; 122,33</t>
+          <t>-20,96; 122,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,62; 52,51</t>
+          <t>-34,15; 51,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,23; 204,49</t>
+          <t>-40,47; 187,88</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 19,47</t>
+          <t>-9,49; 18,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 24,01</t>
+          <t>-9,7; 23,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 17,29</t>
+          <t>-5,7; 17,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 11,06</t>
+          <t>-19,67; 12,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-42,15; 176,94</t>
+          <t>-43,42; 163,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,46; 126,66</t>
+          <t>-28,0; 124,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-48,55; 299,21</t>
+          <t>-42,15; 349,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-54,82; 73,77</t>
+          <t>-54,76; 76,9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,49 +1160,49 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 16,91</t>
+          <t>-7,09; 16,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 2,67</t>
+          <t>-23,38; 3,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 12,28</t>
+          <t>-8,92; 13,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 5,54</t>
+          <t>-19,82; 4,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 137,85</t>
+          <t>-33,25; 129,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,8; 12,93</t>
+          <t>-64,98; 12,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-49,77; 133,49</t>
+          <t>-44,83; 156,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-64,59; 34,99</t>
+          <t>-64,9; 31,95</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 4,45</t>
+          <t>-10,68; 4,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 9,11</t>
+          <t>-5,86; 9,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 8,43</t>
+          <t>-2,41; 8,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 5,66</t>
+          <t>-15,36; 5,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-45,02; 26,27</t>
+          <t>-44,92; 28,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,87; 66,38</t>
+          <t>-27,99; 76,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 181,97</t>
+          <t>-28,74; 153,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-42,02; 25,03</t>
+          <t>-43,21; 27,07</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,28; -0,79</t>
+          <t>-14,5; -0,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 5,49</t>
+          <t>-5,95; 5,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 3,96</t>
+          <t>-7,98; 3,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 3,62</t>
+          <t>-6,22; 3,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,28; -4,17</t>
+          <t>-53,08; -1,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,12; 57,45</t>
+          <t>-37,66; 62,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-44,12; 34,82</t>
+          <t>-43,36; 32,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-62,61; 71,47</t>
+          <t>-63,64; 65,06</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 1,55</t>
+          <t>-4,73; 1,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 3,41</t>
+          <t>-3,8; 3,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 4,82</t>
+          <t>-1,8; 5,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 13,14</t>
+          <t>-2,23; 12,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 8,31</t>
+          <t>-21,96; 9,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 17,62</t>
+          <t>-16,67; 18,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 32,24</t>
+          <t>-10,0; 35,2</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 55,73</t>
+          <t>-8,96; 58,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP15-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 13,77</t>
+          <t>-9,73; 13,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 12,75</t>
+          <t>-13,32; 14,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,26; 11,51</t>
+          <t>-14,81; 11,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 29,14</t>
+          <t>-1,86; 29,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,32; 98,08</t>
+          <t>-38,13; 94,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,98; 58,76</t>
+          <t>-38,9; 69,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-41,24; 54,09</t>
+          <t>-41,84; 53,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 124,77</t>
+          <t>-6,63; 138,75</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 7,03</t>
+          <t>-9,84; 6,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 9,36</t>
+          <t>-8,67; 10,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 15,97</t>
+          <t>-1,14; 16,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 42,55</t>
+          <t>-4,64; 41,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,54; 52,74</t>
+          <t>-44,16; 43,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 52,89</t>
+          <t>-33,36; 62,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 110,41</t>
+          <t>-5,82; 121,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 147,71</t>
+          <t>-12,21; 144,57</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 12,93</t>
+          <t>-7,13; 13,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,38; 3,11</t>
+          <t>-20,95; 3,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 11,74</t>
+          <t>-6,48; 11,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 14,12</t>
+          <t>-12,61; 13,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-40,82; 137,0</t>
+          <t>-38,75; 120,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-55,53; 15,78</t>
+          <t>-56,85; 13,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 152,0</t>
+          <t>-40,34; 183,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-33,66; 61,41</t>
+          <t>-35,29; 54,95</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 12,16</t>
+          <t>-9,62; 11,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 16,8</t>
+          <t>-4,25; 17,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 12,51</t>
+          <t>-13,6; 11,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 14,48</t>
+          <t>-9,29; 15,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-38,3; 80,99</t>
+          <t>-37,43; 71,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,96; 122,33</t>
+          <t>-19,72; 136,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,15; 51,14</t>
+          <t>-34,53; 47,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,47; 187,88</t>
+          <t>-43,94; 185,05</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 18,81</t>
+          <t>-10,45; 18,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 23,48</t>
+          <t>-9,6; 22,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 17,03</t>
+          <t>-7,85; 16,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 12,83</t>
+          <t>-19,45; 13,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,42; 163,41</t>
+          <t>-45,97; 172,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,0; 124,39</t>
+          <t>-28,93; 113,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-42,15; 349,02</t>
+          <t>-51,53; 277,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-54,76; 76,9</t>
+          <t>-56,01; 80,31</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 16,03</t>
+          <t>-7,45; 15,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 3,64</t>
+          <t>-23,61; 4,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 13,64</t>
+          <t>-10,51; 13,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 4,66</t>
+          <t>-20,43; 3,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,25; 129,14</t>
+          <t>-34,18; 126,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,98; 12,39</t>
+          <t>-63,33; 23,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-44,83; 156,38</t>
+          <t>-48,57; 163,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-64,9; 31,95</t>
+          <t>-65,15; 22,91</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 4,51</t>
+          <t>-10,65; 4,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 9,65</t>
+          <t>-5,98; 9,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 8,43</t>
+          <t>-1,95; 8,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 5,7</t>
+          <t>-14,64; 6,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-44,92; 28,26</t>
+          <t>-43,76; 31,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,99; 76,2</t>
+          <t>-27,85; 70,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-28,74; 153,89</t>
+          <t>-25,48; 177,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-43,21; 27,07</t>
+          <t>-43,79; 27,41</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,5; -0,37</t>
+          <t>-15,01; -1,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 5,94</t>
+          <t>-6,24; 5,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 3,75</t>
+          <t>-8,12; 3,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 3,05</t>
+          <t>-6,36; 3,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,08; -1,69</t>
+          <t>-53,8; -5,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-37,66; 62,29</t>
+          <t>-39,25; 60,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-43,36; 32,99</t>
+          <t>-44,81; 33,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-63,64; 65,06</t>
+          <t>-62,06; 65,83</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 1,72</t>
+          <t>-4,82; 1,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 3,59</t>
+          <t>-3,73; 3,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 5,2</t>
+          <t>-2,02; 4,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 12,9</t>
+          <t>-2,81; 12,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-21,96; 9,04</t>
+          <t>-22,21; 9,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 18,49</t>
+          <t>-16,39; 15,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 35,2</t>
+          <t>-10,74; 29,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 58,18</t>
+          <t>-10,98; 57,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP15-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,34</t>
+          <t>6,78</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 13,89</t>
+          <t>-10,09; 13,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 14,65</t>
+          <t>-13,76; 13,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 11,67</t>
+          <t>-14,86; 11,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 29,9</t>
+          <t>-6,56; 20,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-38,13; 94,49</t>
+          <t>-39,26; 88,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-38,9; 69,03</t>
+          <t>-41,25; 63,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-41,84; 53,32</t>
+          <t>-40,41; 49,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 138,75</t>
+          <t>-18,6; 88,25</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,38</t>
+          <t>2,06</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 6,25</t>
+          <t>-9,82; 6,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 10,16</t>
+          <t>-8,98; 9,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 16,66</t>
+          <t>-1,87; 17,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 41,47</t>
+          <t>-10,73; 14,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,16; 43,43</t>
+          <t>-43,44; 47,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,36; 62,11</t>
+          <t>-33,79; 54,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 121,2</t>
+          <t>-9,98; 116,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 144,57</t>
+          <t>-24,96; 45,88</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 13,57</t>
+          <t>-7,21; 12,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 3,89</t>
+          <t>-21,03; 3,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 11,9</t>
+          <t>-7,39; 12,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 13,26</t>
+          <t>-12,35; 14,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 120,78</t>
+          <t>-40,12; 123,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-56,85; 13,89</t>
+          <t>-56,67; 13,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-40,34; 183,55</t>
+          <t>-50,09; 150,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-35,29; 54,95</t>
+          <t>-33,69; 65,96</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>2,82</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 11,04</t>
+          <t>-10,3; 12,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 17,21</t>
+          <t>-4,94; 17,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 11,47</t>
+          <t>-12,62; 12,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 15,21</t>
+          <t>-8,9; 13,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,43; 71,6</t>
+          <t>-38,42; 75,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 136,13</t>
+          <t>-22,19; 122,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,53; 47,99</t>
+          <t>-33,62; 52,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,94; 185,05</t>
+          <t>-41,69; 192,17</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,38</t>
+          <t>-0,91</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-9,08%</t>
+          <t>-3,69%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 18,68</t>
+          <t>-9,72; 19,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 22,7</t>
+          <t>-8,69; 24,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 16,27</t>
+          <t>-7,48; 17,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 13,85</t>
+          <t>-16,97; 13,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-45,97; 172,02</t>
+          <t>-42,15; 176,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,93; 113,47</t>
+          <t>-27,46; 126,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-51,53; 277,88</t>
+          <t>-48,55; 299,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-56,01; 80,31</t>
+          <t>-52,63; 86,36</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-7,58</t>
+          <t>-6,63</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-31,32%</t>
+          <t>-28,37%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 15,69</t>
+          <t>-6,72; 16,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,61; 4,62</t>
+          <t>-24,43; 2,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 13,83</t>
+          <t>-10,67; 12,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 3,47</t>
+          <t>-18,44; 6,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,18; 126,72</t>
+          <t>-30,53; 137,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-63,33; 23,97</t>
+          <t>-65,8; 12,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,57; 163,0</t>
+          <t>-49,77; 133,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,15; 22,91</t>
+          <t>-65,55; 36,42</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-4,51</t>
+          <t>-5,03</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-15,85%</t>
+          <t>-16,92%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 4,69</t>
+          <t>-10,33; 4,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 9,37</t>
+          <t>-6,17; 9,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 8,97</t>
+          <t>-2,02; 8,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 6,25</t>
+          <t>-15,74; 4,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-43,76; 31,35</t>
+          <t>-45,02; 26,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,85; 70,72</t>
+          <t>-27,87; 66,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-25,48; 177,72</t>
+          <t>-21,37; 181,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-43,79; 27,41</t>
+          <t>-43,56; 20,89</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>-1,94</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-17,82%</t>
+          <t>-26,29%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,01; -1,09</t>
+          <t>-14,28; -0,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 5,95</t>
+          <t>-5,87; 5,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 3,94</t>
+          <t>-8,06; 3,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 3,34</t>
+          <t>-6,55; 2,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,8; -5,4</t>
+          <t>-53,28; -4,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,25; 60,33</t>
+          <t>-35,12; 57,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-44,81; 33,57</t>
+          <t>-44,12; 34,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-62,06; 65,83</t>
+          <t>-67,88; 56,01</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>-0,79</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>-3,34%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 1,75</t>
+          <t>-5,16; 1,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 3,14</t>
+          <t>-3,67; 3,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,51</t>
+          <t>-1,48; 4,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 12,94</t>
+          <t>-5,06; 3,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-22,21; 9,43</t>
+          <t>-23,38; 8,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 15,78</t>
+          <t>-16,33; 17,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 29,52</t>
+          <t>-8,09; 32,24</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 57,91</t>
+          <t>-19,07; 15,08</t>
         </is>
       </c>
     </row>
